--- a/governance-copilot/Fargo_Labor_Costs_Confidential.xlsx
+++ b/governance-copilot/Fargo_Labor_Costs_Confidential.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Megan Bowen</t>
+          <t>Lisa Taylor</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -590,7 +590,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Megan Bowen</t>
+          <t>Lisa Taylor</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Anne Weiler</t>
+          <t>Sonia Rees</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -652,7 +652,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Riley Johnson</t>
+          <t>Kai Carter</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Alex Wilber</t>
+          <t>Alex Weyer</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">

--- a/governance-copilot/Fargo_Labor_Costs_Confidential.xlsx
+++ b/governance-copilot/Fargo_Labor_Costs_Confidential.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Lisa Taylor</t>
+          <t>Teresa Sac</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -590,7 +590,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Lisa Taylor</t>
+          <t>Teresa Sac</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -652,7 +652,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Kai Carter</t>
+          <t>Vance DeLeon</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Alex Weyer</t>
+          <t>Billie Vester</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
